--- a/diseases/d085/2000-2004.xlsx
+++ b/diseases/d085/2000-2004.xlsx
@@ -862,7 +862,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -870,17 +870,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -1093,7 +1098,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1101,17 +1106,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1332,17 +1342,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1555,7 +1570,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1563,17 +1578,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1786,7 +1806,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1794,17 +1814,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2017,7 +2042,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -2025,17 +2050,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2248,7 +2278,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -2256,17 +2286,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2479,7 +2514,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2487,17 +2522,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2710,7 +2750,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2718,17 +2758,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2941,7 +2986,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2949,17 +2994,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -3172,7 +3222,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -3180,17 +3230,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -3403,7 +3458,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -3411,17 +3466,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -3634,7 +3694,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -3642,17 +3702,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -3865,7 +3930,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -3873,17 +3938,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -4096,7 +4166,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -4104,17 +4174,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -4327,7 +4402,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -4335,17 +4410,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -4558,7 +4638,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -4566,17 +4646,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -4789,7 +4874,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -4797,17 +4882,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS19" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -5020,7 +5110,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -5028,17 +5118,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -5251,7 +5346,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -5259,17 +5354,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -5482,7 +5582,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -5490,17 +5590,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -5713,7 +5818,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -5721,17 +5826,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -5944,7 +6054,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
@@ -5952,17 +6062,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS24" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -6175,7 +6290,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -6183,17 +6298,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS25" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -6406,7 +6526,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -6414,17 +6534,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS26" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -6637,7 +6762,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -6645,17 +6770,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS27" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -6868,7 +6998,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
@@ -6876,17 +7006,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS28" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -7099,7 +7234,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -7107,17 +7242,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS29" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -7330,7 +7470,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
@@ -7338,17 +7478,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS30" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -7561,7 +7706,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
@@ -7569,17 +7714,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS31" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -7792,7 +7942,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -7800,17 +7950,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS32" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -8023,7 +8178,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
@@ -8031,17 +8186,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS33" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -8254,7 +8414,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -8262,17 +8422,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS34" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -8485,7 +8650,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
@@ -8493,17 +8658,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS35" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -8716,7 +8886,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
@@ -8724,17 +8894,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS36" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -8947,7 +9122,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
@@ -8955,17 +9130,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS37" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -9178,7 +9358,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -9186,17 +9366,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS38" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -9409,7 +9594,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
@@ -9417,17 +9602,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS39" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -9640,7 +9830,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
@@ -9648,17 +9838,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS40" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -9871,7 +10066,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
@@ -9879,17 +10074,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS41" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -10102,7 +10302,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
@@ -10110,17 +10310,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS42" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -10333,7 +10538,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
@@ -10341,17 +10546,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS43" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -10564,7 +10774,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
@@ -10572,17 +10782,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS44" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -10795,7 +11010,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
@@ -10803,17 +11018,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS45" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -11026,7 +11246,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -11034,17 +11254,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -11257,7 +11482,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -11265,17 +11490,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS47" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -11488,7 +11718,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
@@ -11496,17 +11726,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS48" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -11719,7 +11954,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
@@ -11727,17 +11962,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS49" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -11950,7 +12190,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
@@ -11958,17 +12198,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS50" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -12181,7 +12426,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
@@ -12189,17 +12434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS51" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -12412,7 +12662,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -12420,17 +12670,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS52" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -12643,7 +12898,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
@@ -12651,17 +12906,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS53" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -12874,7 +13134,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
@@ -12882,17 +13142,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS54" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -13105,7 +13370,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
@@ -13113,17 +13378,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS55" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -13336,7 +13606,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
@@ -13344,17 +13614,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS56" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -13567,7 +13842,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
@@ -13575,17 +13850,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS57" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -13798,7 +14078,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
@@ -13806,17 +14086,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS58" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -14029,7 +14314,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
@@ -14037,17 +14322,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS59" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -14260,7 +14550,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
@@ -14268,17 +14558,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS60" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -14491,7 +14786,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
@@ -14499,17 +14794,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS61" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
